--- a/df_list_20260308.xlsx
+++ b/df_list_20260308.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-08 04:40:54 KST</t>
+          <t>2026-03-08 07:52:55 KST</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-08 04:40:54 KST</t>
+          <t>2026-03-08 07:52:55 KST</t>
         </is>
       </c>
     </row>

--- a/df_list_20260308.xlsx
+++ b/df_list_20260308.xlsx
@@ -488,7 +488,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>2026-03-08 07:52:55 KST</t>
+          <t>2026-03-08 16:53:11 KST</t>
         </is>
       </c>
     </row>
@@ -523,7 +523,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>2026-03-08 07:52:55 KST</t>
+          <t>2026-03-08 16:53:11 KST</t>
         </is>
       </c>
     </row>
